--- a/KatalonData/RADTestData/JointFilerSSNnoMatch.xlsx
+++ b/KatalonData/RADTestData/JointFilerSSNnoMatch.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="85">
   <si>
     <t>Result</t>
   </si>
@@ -183,6 +183,114 @@
   </si>
   <si>
     <t>Sat Oct 04 16:21:50 EDT 2025</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:54:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:55:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:56:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:15:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:16:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:17:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:09:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:10:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:10:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:11:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:14:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:15:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:16:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:16:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:17:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:18:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:19:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:20:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:20:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:22:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:23:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:24:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:26:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:26:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:27:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:29:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:30:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:40:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:40:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:40:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:41:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:42:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:42:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:47:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:48:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 16:48:29 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -586,10 +694,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>5</v>
@@ -603,10 +711,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>5</v>
@@ -620,10 +728,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>5</v>

--- a/KatalonData/RADTestData/JointFilerSSNnoMatch.xlsx
+++ b/KatalonData/RADTestData/JointFilerSSNnoMatch.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="91">
   <si>
     <t>Result</t>
   </si>
@@ -291,6 +291,24 @@
   </si>
   <si>
     <t>Fri May 22 16:48:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:02:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:02:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:02:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 23:00:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 23:00:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 23:00:34 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -664,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3FE55B8-D1C2-48B9-B410-0ABBCBBE13D8}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" style="2" width="7.42578125" collapsed="true"/>
@@ -693,11 +711,11 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="2">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>82</v>
+      <c r="B2" t="s" s="2">
+        <v>88</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>5</v>
@@ -710,11 +728,11 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="2">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>83</v>
+      <c r="B3" t="s" s="2">
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>5</v>
@@ -727,11 +745,11 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="2">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
-        <v>84</v>
+      <c r="B4" t="s" s="2">
+        <v>90</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>5</v>
